--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.6%</t>
+          <t>-601.5%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-276.5%</t>
         </is>
       </c>
     </row>
@@ -46286,10 +46286,10 @@
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.399840123271741</v>
+        <v>-4.399447395407829</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9966319670959625</v>
+        <v>0.9967890582415269</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.8178254669991903</v>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.0%</t>
+          <t>409.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.5%</t>
+          <t>-613.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-52.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.5%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46286,10 +46286,10 @@
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.399447395407829</v>
+        <v>-4.518899913658187</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9967890582415269</v>
+        <v>0.9490080509413841</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.8178254669991903</v>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-53.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-219.4%</t>
+          <t>-188.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1945"/>
+  <dimension ref="A1:G1946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.436014874910476</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.756924440718406</v>
@@ -46296,6 +46296,29 @@
       </c>
       <c r="G1945" t="n">
         <v>2.266229160518892</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="2" t="n">
+        <v>45408</v>
+      </c>
+      <c r="B1946" t="n">
+        <v>3.436504314863031</v>
+      </c>
+      <c r="C1946" t="n">
+        <v>2.584131532643176</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>-4.518899913658187</v>
+      </c>
+      <c r="E1946" t="n">
+        <v>0.9490080509413841</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>-0.8178254669991903</v>
+      </c>
+      <c r="G1946" t="n">
+        <v>2.577195329629544</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-41.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>137.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-711.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>409.7%</t>
+          <t>433.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.5%</t>
+          <t>-624.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-284.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-64.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-285.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-341.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-166.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-305.8%</t>
+          <t>-302.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-205.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-188.3%</t>
+          <t>-176.2%</t>
         </is>
       </c>
     </row>
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4475588794547782</v>
+        <v>0.3405503747179935</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.296668178233566</v>
+        <v>3.253864776338852</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.653857716665527</v>
+        <v>1.688819569954663</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.110315680764718</v>
+        <v>4.1312927927382</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2655523161318096</v>
+        <v>0.1585438113950249</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.224354691630253</v>
+        <v>3.181551289735538</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.653857716665527</v>
+        <v>1.688819569954663</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.110804819490593</v>
+        <v>4.131781931464074</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.217330049284726</v>
+        <v>0.1103215445479414</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.209145767513086</v>
+        <v>3.166342365618372</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.605635449818444</v>
+        <v>1.64059730310758</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.085951442004009</v>
+        <v>4.10692855397749</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.01980144256506905</v>
+        <v>-0.1268099473018537</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.149234255270709</v>
+        <v>3.106430853375996</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.605635449818444</v>
+        <v>1.64059730310758</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.120892526501551</v>
+        <v>4.141869638475033</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.01476385183748252</v>
+        <v>-0.1217723565742672</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.149826731747082</v>
+        <v>3.107023329852368</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.661279906084761</v>
+        <v>1.696241759373897</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.152856640446679</v>
+        <v>4.173833752420161</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1773899318021211</v>
+        <v>-0.2843984365389057</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.063522681384964</v>
+        <v>3.02071927949025</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.498653826120122</v>
+        <v>1.533615679409258</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.034027374091633</v>
+        <v>4.055004486065115</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2431573218515332</v>
+        <v>-0.3501658265883178</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.038233334495669</v>
+        <v>2.995429932600955</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.498653826120122</v>
+        <v>1.533615679409258</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.035044983222103</v>
+        <v>4.056022095195585</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.3637013103650274</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>2.980643771078027</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.498653826120122</v>
+        <v>1.533615679409258</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.025673015209859</v>
+        <v>4.046650127183341</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.4454732107927791</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>2.938017736862164</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.525689399526259</v>
+        <v>1.560651252815395</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.031977085208779</v>
+        <v>4.05295419718226</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.5126823186646567</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>2.915899410547116</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.525689399526259</v>
+        <v>1.560651252815395</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.036742402042481</v>
+        <v>4.057719514015963</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.7202481030562686</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.830697892909711</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.318123615134647</v>
+        <v>1.353085468423783</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.910027727526755</v>
+        <v>3.931004839500236</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-1.138002126603106</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.66152317499604</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9003695915878102</v>
+        <v>0.935331444876946</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.657302204903716</v>
+        <v>3.678279316877197</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.359624060161223</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.572740618171715</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.897805311189577</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.655629853263698</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.5676281185143</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.494431139384409</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.897805311189577</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.660521997817623</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.779040539402275</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.404947627367207</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.6863928903016019</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.528756001622826</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-2.118198916990798</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.262368575638247</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.3472345127130798</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.318345274376162</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.446216138718277</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.151499976686024</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>0.01921729098560065</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.141873231078443</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-2.939541010253455</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>1.962268778480521</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.08576882325401808</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.08698031294324</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.431926038277552</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.766421159314615</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5781538512781148</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.792655688172514</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.817106429207624</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.610891541755449</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5781538512781148</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.791198226985377</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-4.160789202434287</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.4751875559194</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.686059903305333</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.728223719223663</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.518439552672635</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.328233474480319</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.043710253543681</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.509739567736911</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.827673655668685</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.206312759982158</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.043710253543681</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.511512494437171</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.259479448818473</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>1.019923330189648</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.180127749984948</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.415994884039815</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.494173442951025</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>0.9143305075387174</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.173791482755693</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.408081419379459</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.829836090181478</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.7786460403025015</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.173791482755693</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.406662011035424</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-6.193462335081791</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.6396831025766176</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.272013119622819</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.35421658914939</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.558589717720538</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.4928866645269503</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.568323903921831</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.175684633575814</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-6.967178494901216</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.3282126976694379</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.929292911282166</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.380160979042309</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.1582051364844612</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.924478343753627</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.796552853329307</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>-0.01035756262146048</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.922472394362504</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-8.173229863859151</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.1507696761647188</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.932731085031183</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.51910468584396</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.2930200398129474</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.928830650176878</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.681246956307053</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.3594720279431836</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.97691268110251</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.927235570231879</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-8.977908298117251</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.4743575887380547</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.045655816836388</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.88976866472076</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.411257406227486</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.6517235365165521</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.045655816836388</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.885742360186357</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.794258794970117</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.8050261933351885</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.045655816836388</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.885640258864773</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-9.951657675183238</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.8654142294490068</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.20305469704951</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.79377244670833</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.31118799768724</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-1.003876055152557</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.20305469704951</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.799122750006381</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.63758802635225</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.126520046661385</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.529454725714523</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.61119875276455</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.85673699442645</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.211137883269295</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.74860369378872</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.482751122541801</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.85304606947004</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.209661513286731</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.74860369378872</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.482751122541801</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-11.0573042447999</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.285851586300033</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.876242638402709</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.41168095289205</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.27534201643108</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.368584140468069</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.051013406498608</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.311301046518947</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-11.20187218476363</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.323824506307668</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-2.977543574831159</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.370754647012837</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.37699660215018</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.379319052514768</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.152667992217703</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.280235217328427</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.61144869616466</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.48031905502216</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.152667992217703</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.273016052426831</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.8992525407019</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.602112783611032</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.440471836754941</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.093661554930512</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-12.12907698786573</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.692926772638006</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.603119373825102</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>0.9971888225269723</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.36110590760199</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.783044611903396</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.665132071013525</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9626749328430328</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.30909039363318</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.75824807062947</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.665132071013525</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9666652685294337</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.4507622353573</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.81639203421786</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.665132071013525</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.965190041630692</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.54966897581657</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.840901320236698</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.764038811472801</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.920899407519999</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.35051686857947</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.774291610988541</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.598716285522988</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.007041789443204</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-12.12467171586006</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.674374476864568</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.556789609935824</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.041776867831711</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.83839690353737</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.558725407379431</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.556789609935824</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.042916012387769</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.89129219158166</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.577249748435039</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.551834263847378</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.048522994202945</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.60738346065291</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.457952551824902</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.551834263847378</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.054256698441582</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.49196253651481</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.421521444563529</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.436413339709282</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.113771990530574</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-11.22812566931074</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.325870178994809</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.436413339709282</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.103888509217666</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.96088386844234</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.220808019146823</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.436413339709282</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.102053948718293</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.83757793996412</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.171785962728996</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.346995668581719</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.155404236421369</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.81362439898817</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.161536040193119</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.323042127605762</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.170444867152437</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.54956446066537</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-1.069172381025753</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.058982189282965</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.315620513984363</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.842484837160532</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.7891275652841192</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.058982189282965</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.312833480324062</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.802300538794341</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.7727102220498017</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-3.018797890916774</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.337287683231618</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.722230743256537</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.7413154826139228</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.93872809537897</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.384696381775057</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.488749521026939</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.6399985648842312</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.705246873149372</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.532709543950669</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.309040990883066</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.5710073631396413</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.648075368986676</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.564120236135327</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-9.176765517252178</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.5227296869402593</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.515799895355789</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.638853007060886</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.986165842579025</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.443674756383361</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.325200220682637</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.756027872552415</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.737166043895444</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.3311684956862702</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.325200220682637</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.768934213776073</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.842756033668548</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.5013804211947304</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.430790210455741</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.577604290312992</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.861490935787145</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.4603300401650827</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.430790210455741</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.626148632190078</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.713550894379546</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.5210329462902106</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.410469294547184</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.518462259047045</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.689322257990574</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.5200554779880999</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.386240658158211</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.52428545462695</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.645773851219882</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.5095967273749165</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.386240658158211</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.517324842531857</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.296616953029238</v>
+        <v>-8.403625457766024</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3554716137175156</v>
+        <v>-0.3982750156122301</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.386240658158211</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.531787196913</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.233387581260891</v>
+        <v>-8.340396085997677</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3356477445509816</v>
+        <v>-0.3784511464456961</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.386240658158211</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.526319317372195</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.046899888883884</v>
+        <v>-8.15390839362067</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2635545735896021</v>
+        <v>-0.3063579754843166</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.23471481907034</v>
+        <v>-2.199752965781205</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.614732914835495</v>
+        <v>1.635710026808976</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.025750689980441</v>
+        <v>-8.132759194717227</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2473939157908998</v>
+        <v>-0.2901973176856143</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.178603766877762</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.635123412414886</v>
+        <v>1.656100524388367</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.781985247996997</v>
+        <v>-7.888993752733783</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1541070306504717</v>
+        <v>-0.1969104325451858</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.213565620166897</v>
+        <v>-2.178603766877762</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.630904120761937</v>
+        <v>1.651881232735418</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.517957180803737</v>
+        <v>-7.624965685540523</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.04637148985315154</v>
+        <v>-0.08917489174786608</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.011700221350944</v>
+        <v>-1.976738368061808</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.754147673971525</v>
+        <v>1.775124785945006</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.268106786854663</v>
+        <v>-7.375115291591449</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0463107427101801</v>
+        <v>0.003507340815465998</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.011700221350944</v>
+        <v>-1.976738368061808</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.746889748955227</v>
+        <v>1.767866860928708</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.964539297850684</v>
+        <v>-7.07154780258747</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1713368618324207</v>
+        <v>0.1285334599377062</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.011700221350944</v>
+        <v>-1.976738368061808</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.750488872475876</v>
+        <v>1.771465984449357</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.89105938899867</v>
+        <v>-6.998067893735456</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2140563314277797</v>
+        <v>0.1712529295330651</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.938220312498929</v>
+        <v>-1.903258459209794</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.807904323841638</v>
+        <v>1.828881435815119</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.666026389329847</v>
+        <v>-6.773034894066633</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3030900089116058</v>
+        <v>0.2602866070168917</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.713187312830106</v>
+        <v>-1.678225459540971</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.941944601259229</v>
+        <v>1.96292171323271</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.45139201169344</v>
+        <v>-6.558400516430226</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3936385610204858</v>
+        <v>0.3508351591257717</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.463591081904564</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.07542002889539</v>
+        <v>2.096397140868871</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.184791654719088</v>
+        <v>-6.291800159455875</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4814729625940224</v>
+        <v>0.4386695606993078</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.498552935193699</v>
+        <v>-1.463591081904564</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.056614287679186</v>
+        <v>2.077591399652667</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.944361157914228</v>
+        <v>-6.051369662651014</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5793882379408437</v>
+        <v>0.5365848360461292</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.223160585099704</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.202615662386979</v>
+        <v>2.22359277436046</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.701570350264783</v>
+        <v>-5.808578855001569</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6804338748354422</v>
+        <v>0.6376304729407276</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.258122438388839</v>
+        <v>-1.223160585099704</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.206544976221799</v>
+        <v>2.227522088195281</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.585630500639597</v>
+        <v>-5.692639005376384</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7274883986028562</v>
+        <v>0.6846849967081421</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.14633885408358</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.253316598748814</v>
+        <v>2.274293710722295</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.342974912216434</v>
+        <v>-5.44998341695322</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8215487051921153</v>
+        <v>0.7787453032974008</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.181300707372715</v>
+        <v>-1.14633885408358</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.250314669968807</v>
+        <v>2.271291781942288</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.122954114179423</v>
+        <v>-5.229962618916209</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9111360614175337</v>
+        <v>0.8683326595228191</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.0051190090156</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.33662561402021</v>
+        <v>2.357602725993691</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.923705484274614</v>
+        <v>-5.0307139890114</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.006729696181281</v>
+        <v>0.9639262942865661</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.040080862304735</v>
+        <v>-1.0051190090156</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.352519796822033</v>
+        <v>2.373496908795514</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.764190380755244</v>
+        <v>-4.871198885492031</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.07168158202933</v>
+        <v>1.028878180134616</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8805657587853651</v>
+        <v>-0.8456039054962298</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.449374703373957</v>
+        <v>2.470351815347438</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.619518235655507</v>
+        <v>-4.726526740392293</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.139638542630665</v>
+        <v>1.096835140735951</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7358936136856278</v>
+        <v>-0.7009317603964924</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.546266092995239</v>
+        <v>2.56724320496872</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.601748776724551</v>
+        <v>-4.708757281461337</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.062086018289769</v>
+        <v>1.019282616395055</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7181241547546722</v>
+        <v>-0.6831623014655368</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.472267460440534</v>
+        <v>2.493244572414015</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.514949278945542</v>
+        <v>-4.621957783682328</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.119206310723939</v>
+        <v>1.076402908829225</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7181241547546722</v>
+        <v>-0.6831623014655368</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.4946679537631</v>
+        <v>2.515645065736581</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.41525666421653</v>
+        <v>-4.522265168953316</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.159155757988956</v>
+        <v>1.116352356094241</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6184315400256604</v>
+        <v>-0.583469686736525</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.554555923973919</v>
+        <v>2.5755330359474</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.48362685054054</v>
+        <v>-4.590635355277326</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.142814605934054</v>
+        <v>1.100011204039339</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6091558409894454</v>
+        <v>-0.57419398770031</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.57112826587035</v>
+        <v>2.592105377843831</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.362210420914064</v>
+        <v>-4.46921892565085</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.181817886416536</v>
+        <v>1.139014484521821</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6091558409894454</v>
+        <v>-0.57419398770031</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.561564974502241</v>
+        <v>2.582542086475723</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.393203580242769</v>
+        <v>-4.500212084979555</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9941301877254403</v>
+        <v>0.9513267858307259</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6091558409894454</v>
+        <v>-0.57419398770031</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.386274539542628</v>
+        <v>2.40725165151611</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.217729320450299</v>
+        <v>-4.324737825187086</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.068887123634216</v>
+        <v>1.026083721739502</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6091558409894454</v>
+        <v>-0.57419398770031</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.390841771534416</v>
+        <v>2.411818883507897</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.328665573091548</v>
+        <v>-4.435674077828335</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.024524096464514</v>
+        <v>0.9817206945697996</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6091558409894454</v>
+        <v>-0.57419398770031</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.390853245421213</v>
+        <v>2.411830357394695</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.531692150634782</v>
+        <v>-4.638700655371568</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9464448506671261</v>
+        <v>0.9036414487724118</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8121824185326788</v>
+        <v>-0.7772205652435434</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.272168684115179</v>
+        <v>2.29314579608866</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.373766551699489</v>
+        <v>-4.480775056436275</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019787476673376</v>
+        <v>0.9769840747786613</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8121824185326788</v>
+        <v>-0.7772205652435434</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.282341070547312</v>
+        <v>2.303318182520793</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.522087805510617</v>
+        <v>-4.629096310247403</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9554052457227846</v>
+        <v>0.9126018438280701</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8121824185326788</v>
+        <v>-0.7772205652435434</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.277287341121172</v>
+        <v>2.298264453094653</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.523270890161678</v>
+        <v>-4.630279394898464</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9467077873068859</v>
+        <v>0.9039043854121716</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8178254669991903</v>
+        <v>-0.782863613710055</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.26567728748579</v>
+        <v>2.286654399459272</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.518899913658187</v>
+        <v>-4.625908418394973</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9490080509413841</v>
+        <v>0.9062046490466695</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8178254669991903</v>
+        <v>-0.782863613710055</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.266229160518892</v>
+        <v>2.287206272492373</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.436504314863031</v>
+        <v>3.565276278750032</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.584131532643176</v>
+        <v>2.70556945131942</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.518899913658187</v>
+        <v>-4.625908418394973</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9490080509413841</v>
+        <v>0.9062046490466695</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8178254669991903</v>
+        <v>-0.782863613710055</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.577195329629544</v>
+        <v>2.698633248305788</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-711.0%</t>
+          <t>-711.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>433.7%</t>
+          <t>434.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.2%</t>
+          <t>-612.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-285.6%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-341.4%</t>
+          <t>-341.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-302.3%</t>
+          <t>-302.4%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-205.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3405503747179935</v>
+        <v>0.3392884185234146</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.253864776338852</v>
+        <v>3.25335999386102</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.688819569954663</v>
+        <v>1.687538245488569</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.1312927927382</v>
+        <v>4.130523998058544</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.1585438113950249</v>
+        <v>0.157281855200446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.181551289735538</v>
+        <v>3.181046507257707</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.688819569954663</v>
+        <v>1.687538245488569</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.131781931464074</v>
+        <v>4.131013136784418</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1103215445479414</v>
+        <v>0.1090595883533625</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.166342365618372</v>
+        <v>3.165837583140541</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.64059730310758</v>
+        <v>1.639315978641486</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.10692855397749</v>
+        <v>4.106159759297834</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1268099473018537</v>
+        <v>-0.1280719034964326</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.106430853375996</v>
+        <v>3.105926070898164</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.64059730310758</v>
+        <v>1.639315978641486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.141869638475033</v>
+        <v>4.141100843795376</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1217723565742672</v>
+        <v>-0.1230343127688461</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.107023329852368</v>
+        <v>3.106518547374537</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.696241759373897</v>
+        <v>1.694960434907803</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.173833752420161</v>
+        <v>4.173064957740505</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2843984365389057</v>
+        <v>-0.2856603927334846</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.02071927949025</v>
+        <v>3.020214497012419</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.533615679409258</v>
+        <v>1.532334354943165</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.055004486065115</v>
+        <v>4.054235691385458</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3501658265883178</v>
+        <v>-0.3514277827828967</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.995429932600955</v>
+        <v>2.994925150123124</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.533615679409258</v>
+        <v>1.532334354943165</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.056022095195585</v>
+        <v>4.055253300515929</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3637013103650274</v>
+        <v>-0.3649632665596063</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.980643771078027</v>
+        <v>2.980138988600196</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.533615679409258</v>
+        <v>1.532334354943165</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.046650127183341</v>
+        <v>4.045881332503685</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4454732107927791</v>
+        <v>-0.446735166987358</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.938017736862164</v>
+        <v>2.937512954384333</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.560651252815395</v>
+        <v>1.559369928349301</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.05295419718226</v>
+        <v>4.052185402502604</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5126823186646567</v>
+        <v>-0.5139442748592357</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.915899410547116</v>
+        <v>2.915394628069284</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.560651252815395</v>
+        <v>1.559369928349301</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.057719514015963</v>
+        <v>4.056950719336307</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7202481030562686</v>
+        <v>-0.7215100592508475</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.830697892909711</v>
+        <v>2.83019311043188</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.353085468423783</v>
+        <v>1.351804143957689</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.931004839500236</v>
+        <v>3.93023604482058</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.138002126603106</v>
+        <v>-1.139264082797685</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.66152317499604</v>
+        <v>2.661018392518208</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.935331444876946</v>
+        <v>0.9340501204108523</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.678279316877197</v>
+        <v>3.677510522197541</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.359624060161223</v>
+        <v>-1.360886016355802</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.572740618171715</v>
+        <v>2.572235835693883</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.897805311189577</v>
+        <v>0.8965239867234833</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.655629853263698</v>
+        <v>3.654861058584042</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.5676281185143</v>
+        <v>-1.568890074708879</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.494431139384409</v>
+        <v>2.493926356906577</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.897805311189577</v>
+        <v>0.8965239867234833</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.660521997817623</v>
+        <v>3.659753203137967</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.779040539402275</v>
+        <v>-1.780302495596854</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.404947627367207</v>
+        <v>2.404442844889375</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6863928903016019</v>
+        <v>0.6851115658355083</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.528756001622826</v>
+        <v>3.52798720694317</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.118198916990798</v>
+        <v>-2.119460873185377</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.262368575638247</v>
+        <v>2.261863793160416</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3472345127130798</v>
+        <v>0.3459531882469862</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.318345274376162</v>
+        <v>3.317576479696505</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.446216138718277</v>
+        <v>-2.447478094912856</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.151499976686024</v>
+        <v>2.150995194208193</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.01921729098560065</v>
+        <v>0.01793596651950702</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.141873231078443</v>
+        <v>3.141104436398786</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.939541010253455</v>
+        <v>-2.940802966448034</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.962268778480521</v>
+        <v>1.96176399600269</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.08576882325401808</v>
+        <v>-0.08705014772011171</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.08698031294324</v>
+        <v>3.086211518263584</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.431926038277552</v>
+        <v>-3.433187994472131</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.766421159314615</v>
+        <v>1.765916376836783</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.5781538512781148</v>
+        <v>-0.5794351757442084</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.792655688172514</v>
+        <v>2.791886893492858</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.817106429207624</v>
+        <v>-3.818368385402203</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.610891541755449</v>
+        <v>1.610386759277617</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.5781538512781148</v>
+        <v>-0.5794351757442084</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.791198226985377</v>
+        <v>2.790429432305721</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.160789202434287</v>
+        <v>-4.162051158628866</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.4751875559194</v>
+        <v>1.474682773441569</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.686059903305333</v>
+        <v>-0.6873412277714266</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.728223719223663</v>
+        <v>2.727454924544007</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.518439552672635</v>
+        <v>-4.519701508867214</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.328233474480319</v>
+        <v>1.327728692002487</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.043710253543681</v>
+        <v>-1.044991578009775</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.509739567736911</v>
+        <v>2.508970773057255</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.827673655668685</v>
+        <v>-4.828935611863264</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.206312759982158</v>
+        <v>1.205807977504326</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.043710253543681</v>
+        <v>-1.044991578009775</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.511512494437171</v>
+        <v>2.510743699757515</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.259479448818473</v>
+        <v>-5.260741405013052</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.019923330189648</v>
+        <v>1.019418547711816</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.180127749984948</v>
+        <v>-1.181409074451042</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.415994884039815</v>
+        <v>2.415226089360159</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.494173442951025</v>
+        <v>-5.495435399145604</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9143305075387174</v>
+        <v>0.9138257250608857</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.173791482755693</v>
+        <v>-1.175072807221786</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.408081419379459</v>
+        <v>2.407312624699803</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.829836090181478</v>
+        <v>-5.831098046376057</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7786460403025015</v>
+        <v>0.7781412578246698</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.173791482755693</v>
+        <v>-1.175072807221786</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.406662011035424</v>
+        <v>2.405893216355768</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.193462335081791</v>
+        <v>-6.19472429127637</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6396831025766176</v>
+        <v>0.6391783200987859</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.272013119622819</v>
+        <v>-1.273294444088912</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.35421658914939</v>
+        <v>2.353447794469734</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.558589717720538</v>
+        <v>-6.559851673915117</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4928866645269503</v>
+        <v>0.4923818820491186</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.568323903921831</v>
+        <v>-1.569605228387925</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.175684633575814</v>
+        <v>2.174915838896158</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.967178494901216</v>
+        <v>-6.968440451095795</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3282126976694379</v>
+        <v>0.3277079151916062</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.929292911282166</v>
+        <v>1.92852411660251</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.380160979042309</v>
+        <v>-7.381422935236889</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1582051364844612</v>
+        <v>0.1577003540066295</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.924478343753627</v>
+        <v>1.923709549073971</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.796552853329307</v>
+        <v>-7.797814809523886</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.01035756262146048</v>
+        <v>-0.01086234509929218</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.922472394362504</v>
+        <v>1.921703599682848</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.173229863859151</v>
+        <v>-8.17449182005373</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1507696761647188</v>
+        <v>-0.1512744586425505</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.932731085031183</v>
+        <v>1.931962290351527</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.51910468584396</v>
+        <v>-8.520366642038539</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2930200398129474</v>
+        <v>-0.2935248222907791</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.928830650176878</v>
+        <v>1.928061855497222</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.681246956307053</v>
+        <v>-8.682508912501632</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3594720279431836</v>
+        <v>-0.3599768104210153</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.97691268110251</v>
+        <v>-1.978194005568603</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.927235570231879</v>
+        <v>1.926466775552223</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.977908298117251</v>
+        <v>-8.97917025431183</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4743575887380547</v>
+        <v>-0.4748623712158864</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.045655816836388</v>
+        <v>-2.046937141302482</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.88976866472076</v>
+        <v>1.888999870041104</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.411257406227486</v>
+        <v>-9.412519362422065</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6517235365165521</v>
+        <v>-0.6522283189943838</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.045655816836388</v>
+        <v>-2.046937141302482</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.885742360186357</v>
+        <v>1.884973565506701</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.794258794970117</v>
+        <v>-9.795520751164696</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8050261933351885</v>
+        <v>-0.8055309758130202</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.045655816836388</v>
+        <v>-2.046937141302482</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.885640258864773</v>
+        <v>1.884871464185117</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.951657675183238</v>
+        <v>-9.952919631377817</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8654142294490068</v>
+        <v>-0.8659190119268385</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.20305469704951</v>
+        <v>-2.204336021515603</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.79377244670833</v>
+        <v>1.793003652028674</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.31118799768724</v>
+        <v>-10.31244995388182</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.003876055152557</v>
+        <v>-1.004380837630388</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.20305469704951</v>
+        <v>-2.204336021515603</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.799122750006381</v>
+        <v>1.798353955326724</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.63758802635225</v>
+        <v>-10.63884998254683</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.126520046661385</v>
+        <v>-1.127024829139217</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.529454725714523</v>
+        <v>-2.530736050180616</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.61119875276455</v>
+        <v>1.610429958084894</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.85673699442645</v>
+        <v>-10.85799895062103</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.211137883269295</v>
+        <v>-1.211642665747127</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.74860369378872</v>
+        <v>-2.749885018254814</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.482751122541801</v>
+        <v>1.481982327862145</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.85304606947004</v>
+        <v>-10.85430802566462</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.209661513286731</v>
+        <v>-1.210166295764563</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.74860369378872</v>
+        <v>-2.749885018254814</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.482751122541801</v>
+        <v>1.481982327862145</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.0573042447999</v>
+        <v>-11.05856620099448</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.285851586300033</v>
+        <v>-1.286356368777866</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.876242638402709</v>
+        <v>-2.877523962868803</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.41168095289205</v>
+        <v>1.410912158212394</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.27534201643108</v>
+        <v>-11.27660397262566</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.368584140468069</v>
+        <v>-1.3690889229459</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.051013406498608</v>
+        <v>-3.052294730964701</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.311301046518947</v>
+        <v>1.31053225183929</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.20187218476363</v>
+        <v>-11.20313414095821</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.323824506307668</v>
+        <v>-1.3243292887855</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.977543574831159</v>
+        <v>-2.978824899297253</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.370754647012837</v>
+        <v>1.36998585233318</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.37699660215018</v>
+        <v>-11.37825855834475</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.379319052514768</v>
+        <v>-1.3798238349926</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.152667992217703</v>
+        <v>-3.153949316683797</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.280235217328427</v>
+        <v>1.279466422648771</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.61144869616466</v>
+        <v>-11.61271065235924</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.48031905502216</v>
+        <v>-1.480823837499992</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.152667992217703</v>
+        <v>-3.153949316683797</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.273016052426831</v>
+        <v>1.272247257747175</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.8992525407019</v>
+        <v>-11.90051449689648</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.602112783611032</v>
+        <v>-1.602617566088864</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.440471836754941</v>
+        <v>-3.441753161221035</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.093661554930512</v>
+        <v>1.092892760250856</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.12907698786573</v>
+        <v>-12.13033894406031</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.692926772638006</v>
+        <v>-1.693431555115837</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.603119373825102</v>
+        <v>-3.604400698291196</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9971888225269723</v>
+        <v>0.9964200278473161</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.36110590760199</v>
+        <v>-12.36236786379657</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.783044611903396</v>
+        <v>-1.783549394381228</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.665132071013525</v>
+        <v>-3.666413395479619</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9626749328430328</v>
+        <v>0.9619061381633767</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.30909039363318</v>
+        <v>-12.31035234982776</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.75824807062947</v>
+        <v>-1.758752853107302</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.665132071013525</v>
+        <v>-3.666413395479619</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9666652685294337</v>
+        <v>0.9658964738497775</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.4507622353573</v>
+        <v>-12.45202419155188</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.81639203421786</v>
+        <v>-1.816896816695691</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.665132071013525</v>
+        <v>-3.666413395479619</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.965190041630692</v>
+        <v>0.9644212469510358</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.54966897581657</v>
+        <v>-12.55093093201115</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.840901320236698</v>
+        <v>-1.841406102714529</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.764038811472801</v>
+        <v>-3.765320135938894</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.920899407519999</v>
+        <v>0.9201306128403428</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.35051686857947</v>
+        <v>-12.35177882477405</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.774291610988541</v>
+        <v>-1.774796393466373</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.598716285522988</v>
+        <v>-3.599997609989081</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.007041789443204</v>
+        <v>1.006272994763548</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.12467171586006</v>
+        <v>-12.12593367205464</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.674374476864568</v>
+        <v>-1.6748792593424</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.556789609935824</v>
+        <v>-3.558070934401917</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.041776867831711</v>
+        <v>1.041008073152054</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.83839690353737</v>
+        <v>-11.83965885973195</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.558725407379431</v>
+        <v>-1.559230189857263</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.556789609935824</v>
+        <v>-3.558070934401917</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.042916012387769</v>
+        <v>1.042147217708113</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.89129219158166</v>
+        <v>-11.89255414777623</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.577249748435039</v>
+        <v>-1.57775453091287</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.551834263847378</v>
+        <v>-3.553115588313471</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.048522994202945</v>
+        <v>1.047754199523289</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.60738346065291</v>
+        <v>-11.60864541684749</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.457952551824902</v>
+        <v>-1.458457334302734</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.551834263847378</v>
+        <v>-3.553115588313471</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.054256698441582</v>
+        <v>1.053487903761925</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.49196253651481</v>
+        <v>-11.49322449270939</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.421521444563529</v>
+        <v>-1.422026227041361</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.436413339709282</v>
+        <v>-3.437694664175376</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.113771990530574</v>
+        <v>1.113003195850918</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.22812566931074</v>
+        <v>-11.22938762550532</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.325870178994809</v>
+        <v>-1.32637496147264</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.436413339709282</v>
+        <v>-3.437694664175376</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.103888509217666</v>
+        <v>1.10311971453801</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.96088386844234</v>
+        <v>-10.96214582463692</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.220808019146823</v>
+        <v>-1.221312801624655</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.436413339709282</v>
+        <v>-3.437694664175376</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.102053948718293</v>
+        <v>1.101285154038636</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.83757793996412</v>
+        <v>-10.8388398961587</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.171785962728996</v>
+        <v>-1.172290745206829</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.346995668581719</v>
+        <v>-3.348276993047813</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.155404236421369</v>
+        <v>1.154635441741713</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.81362439898817</v>
+        <v>-10.81488635518274</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.161536040193119</v>
+        <v>-1.162040822670952</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.323042127605762</v>
+        <v>-3.324323452071855</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.170444867152437</v>
+        <v>1.169676072472781</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.54956446066537</v>
+        <v>-10.55082641685995</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.069172381025753</v>
+        <v>-1.069677163503584</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.058982189282965</v>
+        <v>-3.060263513749059</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.315620513984363</v>
+        <v>1.314851719304707</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.842484837160532</v>
+        <v>-9.843746793355111</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7891275652841192</v>
+        <v>-0.7896323477619509</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.058982189282965</v>
+        <v>-3.060263513749059</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.312833480324062</v>
+        <v>1.312064685644406</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.802300538794341</v>
+        <v>-9.80356249498892</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7727102220498017</v>
+        <v>-0.7732150045276334</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.018797890916774</v>
+        <v>-3.020079215382868</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.337287683231618</v>
+        <v>1.336518888551962</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.722230743256537</v>
+        <v>-9.723492699451116</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7413154826139228</v>
+        <v>-0.7418202650917545</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.93872809537897</v>
+        <v>-2.940009419845064</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.384696381775057</v>
+        <v>1.383927587095401</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.488749521026939</v>
+        <v>-9.490011477221518</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6399985648842312</v>
+        <v>-0.6405033473620629</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.705246873149372</v>
+        <v>-2.706528197615465</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.532709543950669</v>
+        <v>1.531940749271013</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.309040990883066</v>
+        <v>-9.310302947077645</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5710073631396413</v>
+        <v>-0.571512145617473</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.648075368986676</v>
+        <v>-2.649356693452769</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.564120236135327</v>
+        <v>1.563351441455671</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.176765517252178</v>
+        <v>-9.178027473446758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5227296869402593</v>
+        <v>-0.523234469418091</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.515799895355789</v>
+        <v>-2.517081219821883</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.638853007060886</v>
+        <v>1.63808421238123</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.986165842579025</v>
+        <v>-8.987427798773604</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.443674756383361</v>
+        <v>-0.4441795388611927</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.325200220682637</v>
+        <v>-2.32648154514873</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.756027872552415</v>
+        <v>1.755259077872758</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.737166043895444</v>
+        <v>-8.738428000090023</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3311684956862702</v>
+        <v>-0.3316732781641014</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.325200220682637</v>
+        <v>-2.32648154514873</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.768934213776073</v>
+        <v>1.768165419096417</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.842756033668548</v>
+        <v>-8.844017989863127</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5013804211947304</v>
+        <v>-0.5018852036725621</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.430790210455741</v>
+        <v>-2.432071534921835</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.577604290312992</v>
+        <v>1.576835495633336</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.861490935787145</v>
+        <v>-8.862752891981724</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4603300401650827</v>
+        <v>-0.4608348226429144</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.430790210455741</v>
+        <v>-2.432071534921835</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.626148632190078</v>
+        <v>1.625379837510422</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.713550894379546</v>
+        <v>-8.714812850574125</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5210329462902106</v>
+        <v>-0.5215377287680423</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.410469294547184</v>
+        <v>-2.411750619013277</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.518462259047045</v>
+        <v>1.517693464367389</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.689322257990574</v>
+        <v>-8.690584214185153</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5200554779880999</v>
+        <v>-0.5205602604659316</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.386240658158211</v>
+        <v>-2.387521982624305</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.52428545462695</v>
+        <v>1.523516659947294</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.645773851219882</v>
+        <v>-8.647035807414461</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5095967273749165</v>
+        <v>-0.5101015098527482</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.386240658158211</v>
+        <v>-2.387521982624305</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.517324842531857</v>
+        <v>1.516556047852201</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.403625457766024</v>
+        <v>-8.404887413960603</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3982750156122301</v>
+        <v>-0.3987797980900618</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.386240658158211</v>
+        <v>-2.387521982624305</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.531787196913</v>
+        <v>1.531018402233344</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.340396085997677</v>
+        <v>-8.341658042192256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3784511464456961</v>
+        <v>-0.3789559289235278</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.386240658158211</v>
+        <v>-2.387521982624305</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.526319317372195</v>
+        <v>1.525550522692539</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.15390839362067</v>
+        <v>-8.155170349815249</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3063579754843166</v>
+        <v>-0.3068627579621483</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.199752965781205</v>
+        <v>-2.201034290247299</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.635710026808976</v>
+        <v>1.63494123212932</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.132759194717227</v>
+        <v>-8.134021150911806</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2901973176856143</v>
+        <v>-0.290702100163446</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.178603766877762</v>
+        <v>-2.179885091343855</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.656100524388367</v>
+        <v>1.655331729708711</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.888993752733783</v>
+        <v>-7.890255708928362</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1969104325451858</v>
+        <v>-0.1974152150230175</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.178603766877762</v>
+        <v>-2.179885091343855</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.651881232735418</v>
+        <v>1.651112438055762</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.624965685540523</v>
+        <v>-7.626227641735102</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08917489174786608</v>
+        <v>-0.08967967422569778</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.976738368061808</v>
+        <v>-1.978019692527902</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.775124785945006</v>
+        <v>1.77435599126535</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.375115291591449</v>
+        <v>-7.376377247786028</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.003507340815465998</v>
+        <v>0.003002558337634298</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.976738368061808</v>
+        <v>-1.978019692527902</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.767866860928708</v>
+        <v>1.767098066249052</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.07154780258747</v>
+        <v>-7.072809758782049</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1285334599377062</v>
+        <v>0.1280286774598745</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.976738368061808</v>
+        <v>-1.978019692527902</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.771465984449357</v>
+        <v>1.770697189769701</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.998067893735456</v>
+        <v>-6.999329849930035</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1712529295330651</v>
+        <v>0.1707481470552339</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.903258459209794</v>
+        <v>-1.904539783675887</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.828881435815119</v>
+        <v>1.828112641135463</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.773034894066633</v>
+        <v>-6.774296850261212</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2602866070168917</v>
+        <v>0.25978182453906</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.678225459540971</v>
+        <v>-1.679506784007065</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.96292171323271</v>
+        <v>1.962152918553054</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.558400516430226</v>
+        <v>-6.559662472624805</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3508351591257717</v>
+        <v>0.35033037664794</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.463591081904564</v>
+        <v>-1.464872406370658</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.096397140868871</v>
+        <v>2.095628346189215</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.291800159455875</v>
+        <v>-6.293062115650454</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4386695606993078</v>
+        <v>0.4381647782214761</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.463591081904564</v>
+        <v>-1.464872406370658</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.077591399652667</v>
+        <v>2.076822604973011</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.051369662651014</v>
+        <v>-6.052631618845593</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5365848360461292</v>
+        <v>0.5360800535682979</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.223160585099704</v>
+        <v>-1.224441909565797</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.22359277436046</v>
+        <v>2.222823979680804</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.808578855001569</v>
+        <v>-5.809840811196148</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6376304729407276</v>
+        <v>0.6371256904628964</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.223160585099704</v>
+        <v>-1.224441909565797</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.227522088195281</v>
+        <v>2.226753293515625</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.692639005376384</v>
+        <v>-5.693900961570963</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6846849967081421</v>
+        <v>0.6841802142303104</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.14633885408358</v>
+        <v>-1.147620178549674</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.274293710722295</v>
+        <v>2.273524916042639</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.44998341695322</v>
+        <v>-5.451245373147799</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7787453032974008</v>
+        <v>0.7782405208195691</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.14633885408358</v>
+        <v>-1.147620178549674</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.271291781942288</v>
+        <v>2.270522987262632</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.229962618916209</v>
+        <v>-5.231224575110788</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8683326595228191</v>
+        <v>0.8678278770449874</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.0051190090156</v>
+        <v>-1.006400333481693</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.357602725993691</v>
+        <v>2.356833931314035</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.0307139890114</v>
+        <v>-5.031975945205979</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9639262942865661</v>
+        <v>0.9634215118087344</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.0051190090156</v>
+        <v>-1.006400333481693</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.373496908795514</v>
+        <v>2.372728114115858</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.871198885492031</v>
+        <v>-4.87246084168661</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.028878180134616</v>
+        <v>1.028373397656784</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8456039054962298</v>
+        <v>-0.8468852299623234</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.470351815347438</v>
+        <v>2.469583020667782</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.726526740392293</v>
+        <v>-4.727788696586872</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.096835140735951</v>
+        <v>1.096330358258119</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7009317603964924</v>
+        <v>-0.702213084862586</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.56724320496872</v>
+        <v>2.566474410289064</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.708757281461337</v>
+        <v>-4.710019237655916</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.019282616395055</v>
+        <v>1.018777833917223</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6831623014655368</v>
+        <v>-0.6844436259316304</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.493244572414015</v>
+        <v>2.492475777734359</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.621957783682328</v>
+        <v>-4.623219739876907</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.076402908829225</v>
+        <v>1.075898126351393</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6831623014655368</v>
+        <v>-0.6844436259316304</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.515645065736581</v>
+        <v>2.514876271056925</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.522265168953316</v>
+        <v>-4.523527125147895</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.116352356094241</v>
+        <v>1.11584757361641</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.583469686736525</v>
+        <v>-0.5847510112026186</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.5755330359474</v>
+        <v>2.574764241267744</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.590635355277326</v>
+        <v>-4.591897311471905</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.100011204039339</v>
+        <v>1.099506421561508</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.57419398770031</v>
+        <v>-0.5754753121664037</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.592105377843831</v>
+        <v>2.591336583164175</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.46921892565085</v>
+        <v>-4.470480881845429</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.139014484521821</v>
+        <v>1.13850970204399</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.57419398770031</v>
+        <v>-0.5754753121664037</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.582542086475723</v>
+        <v>2.581773291796067</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.500212084979555</v>
+        <v>-4.501474041174134</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9513267858307259</v>
+        <v>0.9508220033528942</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.57419398770031</v>
+        <v>-0.5754753121664037</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.40725165151611</v>
+        <v>2.406482856836453</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.324737825187086</v>
+        <v>-4.325999781381665</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.026083721739502</v>
+        <v>1.02557893926167</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.57419398770031</v>
+        <v>-0.5754753121664037</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.411818883507897</v>
+        <v>2.411050088828241</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.435674077828335</v>
+        <v>-4.436936034022914</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9817206945697996</v>
+        <v>0.9812159120919679</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.57419398770031</v>
+        <v>-0.5754753121664037</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.411830357394695</v>
+        <v>2.411061562715039</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.638700655371568</v>
+        <v>-4.639962611566147</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9036414487724118</v>
+        <v>0.9031366662945801</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7772205652435434</v>
+        <v>-0.7785018897096371</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.29314579608866</v>
+        <v>2.292377001409004</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.480775056436275</v>
+        <v>-4.482037012630854</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9769840747786613</v>
+        <v>0.9764792923008296</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7772205652435434</v>
+        <v>-0.7785018897096371</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.303318182520793</v>
+        <v>2.302549387841136</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.629096310247403</v>
+        <v>-4.630358266441982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9126018438280701</v>
+        <v>0.9120970613502386</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7772205652435434</v>
+        <v>-0.7785018897096371</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.298264453094653</v>
+        <v>2.297495658414997</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.630279394898464</v>
+        <v>-4.631541351093043</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9039043854121716</v>
+        <v>0.9033996029343399</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.782863613710055</v>
+        <v>-0.7841449381761486</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.286654399459272</v>
+        <v>2.285885604779616</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.625908418394973</v>
+        <v>-4.50841364409896</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9062046490466695</v>
+        <v>0.9532025587650748</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.782863613710055</v>
+        <v>-0.7841449381761486</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.287206272492373</v>
+        <v>2.286437477812717</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,13 +46309,13 @@
         <v>2.70556945131942</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.625908418394973</v>
+        <v>-4.50841364409896</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9062046490466695</v>
+        <v>0.9532025587650748</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.782863613710055</v>
+        <v>-0.7841449381761486</v>
       </c>
       <c r="G1946" t="n">
         <v>2.698633248305788</v>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-36.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.0%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-711.1%</t>
+          <t>-700.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>434.2%</t>
+          <t>410.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-612.4%</t>
+          <t>-601.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-284.8%</t>
+          <t>-280.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.9%</t>
+          <t>-276.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-341.5%</t>
+          <t>-344.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.4%</t>
+          <t>-167.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-302.4%</t>
+          <t>-292.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-205.3%</t>
+          <t>-207.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.2%</t>
+          <t>-211.9%</t>
         </is>
       </c>
     </row>
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3392884185234146</v>
+        <v>0.4475588794547782</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.25335999386102</v>
+        <v>3.296668178233566</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.687538245488569</v>
+        <v>1.653857716665527</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.130523998058544</v>
+        <v>4.110315680764718</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.157281855200446</v>
+        <v>0.2655523161318096</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.181046507257707</v>
+        <v>3.224354691630253</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.687538245488569</v>
+        <v>1.653857716665527</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.131013136784418</v>
+        <v>4.110804819490593</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1090595883533625</v>
+        <v>0.217330049284726</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.165837583140541</v>
+        <v>3.209145767513086</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.639315978641486</v>
+        <v>1.605635449818444</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.106159759297834</v>
+        <v>4.085951442004009</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1280719034964326</v>
+        <v>-0.01980144256506905</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.105926070898164</v>
+        <v>3.149234255270709</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.639315978641486</v>
+        <v>1.605635449818444</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.141100843795376</v>
+        <v>4.120892526501551</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1230343127688461</v>
+        <v>-0.01476385183748252</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.106518547374537</v>
+        <v>3.149826731747082</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.694960434907803</v>
+        <v>1.661279906084761</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.173064957740505</v>
+        <v>4.152856640446679</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2856603927334846</v>
+        <v>-0.1773899318021211</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.020214497012419</v>
+        <v>3.063522681384964</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.532334354943165</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.054235691385458</v>
+        <v>4.034027374091633</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3514277827828967</v>
+        <v>-0.2431573218515332</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.994925150123124</v>
+        <v>3.038233334495669</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.532334354943165</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.055253300515929</v>
+        <v>4.035044983222103</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3649632665596063</v>
+        <v>-0.2566928056282428</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.980138988600196</v>
+        <v>3.023447172972741</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.532334354943165</v>
+        <v>1.498653826120122</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.045881332503685</v>
+        <v>4.025673015209859</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.446735166987358</v>
+        <v>-0.3384647060559944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.937512954384333</v>
+        <v>2.980821138756879</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.559369928349301</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.052185402502604</v>
+        <v>4.031977085208779</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5139442748592357</v>
+        <v>-0.4056738139278721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.915394628069284</v>
+        <v>2.95870281244183</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.559369928349301</v>
+        <v>1.525689399526259</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.056950719336307</v>
+        <v>4.036742402042481</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7215100592508475</v>
+        <v>-0.613239598319484</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.83019311043188</v>
+        <v>2.873501294804425</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.351804143957689</v>
+        <v>1.318123615134647</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.93023604482058</v>
+        <v>3.910027727526755</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.139264082797685</v>
+        <v>-1.030993621866321</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.661018392518208</v>
+        <v>2.704326576890754</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9340501204108523</v>
+        <v>0.9003695915878102</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.677510522197541</v>
+        <v>3.657302204903716</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.360886016355802</v>
+        <v>-1.252615555424438</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.572235835693883</v>
+        <v>2.615544020066428</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8965239867234833</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.654861058584042</v>
+        <v>3.634652741290216</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.568890074708879</v>
+        <v>-1.460619613777516</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.493926356906577</v>
+        <v>2.537234541279123</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8965239867234833</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.659753203137967</v>
+        <v>3.639544885844141</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.780302495596854</v>
+        <v>-1.672032034665491</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.404442844889375</v>
+        <v>2.447751029261921</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6851115658355083</v>
+        <v>0.6514310370124661</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.52798720694317</v>
+        <v>3.507778889649344</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.119460873185377</v>
+        <v>-2.011190412254013</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.261863793160416</v>
+        <v>2.305171977532961</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3459531882469862</v>
+        <v>0.312272659423944</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.317576479696505</v>
+        <v>3.29736816240268</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.447478094912856</v>
+        <v>-2.339207633981492</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.150995194208193</v>
+        <v>2.194303378580738</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.01793596651950702</v>
+        <v>-0.01574456230353516</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.141104436398786</v>
+        <v>3.120896119104961</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.940802966448034</v>
+        <v>-2.83253250551667</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.96176399600269</v>
+        <v>2.005072180375235</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.08705014772011171</v>
+        <v>-0.1207306765431539</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.086211518263584</v>
+        <v>3.066003200969758</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.433187994472131</v>
+        <v>-3.324917533540767</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.765916376836783</v>
+        <v>1.809224561209329</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.5794351757442084</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.791886893492858</v>
+        <v>2.771678576199033</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.818368385402203</v>
+        <v>-3.71009792447084</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.610386759277617</v>
+        <v>1.653694943650163</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.5794351757442084</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.790429432305721</v>
+        <v>2.770221115011896</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.162051158628866</v>
+        <v>-4.053780697697502</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.474682773441569</v>
+        <v>1.517990957814114</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.6873412277714266</v>
+        <v>-0.7210217565944688</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.727454924544007</v>
+        <v>2.707246607250181</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.519701508867214</v>
+        <v>-4.41143104793585</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.327728692002487</v>
+        <v>1.371036876375032</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.044991578009775</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.508970773057255</v>
+        <v>2.48876245576343</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.828935611863264</v>
+        <v>-4.720665150931901</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.205807977504326</v>
+        <v>1.249116161876872</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.044991578009775</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.510743699757515</v>
+        <v>2.49053538246369</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.260741405013052</v>
+        <v>-5.152470944081688</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.019418547711816</v>
+        <v>1.062726732084361</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.181409074451042</v>
+        <v>-1.215089603274084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.415226089360159</v>
+        <v>2.395017772066334</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.495435399145604</v>
+        <v>-5.387164938214241</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9138257250608857</v>
+        <v>0.957133909433431</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.175072807221786</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.407312624699803</v>
+        <v>2.387104307405978</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.831098046376057</v>
+        <v>-5.722827585444693</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7781412578246698</v>
+        <v>0.8214494421972152</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.175072807221786</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.405893216355768</v>
+        <v>2.385684899061943</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.19472429127637</v>
+        <v>-6.086453830345007</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6391783200987859</v>
+        <v>0.6824865044713313</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.273294444088912</v>
+        <v>-1.306974972911954</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.353447794469734</v>
+        <v>2.333239477175909</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.559851673915117</v>
+        <v>-6.451581212983753</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4923818820491186</v>
+        <v>0.5356900664216639</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.569605228387925</v>
+        <v>-1.603285757210967</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.174915838896158</v>
+        <v>2.154707521602333</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.968440451095795</v>
+        <v>-6.860169990164431</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3277079151916062</v>
+        <v>0.3710160995641516</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.92852411660251</v>
+        <v>1.908315799308685</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.381422935236889</v>
+        <v>-7.273152474305525</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1577003540066295</v>
+        <v>0.2010085383791749</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.923709549073971</v>
+        <v>1.903501231780145</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.797814809523886</v>
+        <v>-7.689544348592523</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.01086234509929218</v>
+        <v>0.03244583927325317</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.921703599682848</v>
+        <v>1.901495282389023</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.17449182005373</v>
+        <v>-8.066221359122366</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1512744586425505</v>
+        <v>-0.1079662742700052</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.931962290351527</v>
+        <v>1.911753973057702</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.520366642038539</v>
+        <v>-8.412096181107175</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2935248222907791</v>
+        <v>-0.2502166379182338</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.928061855497222</v>
+        <v>1.907853538203397</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.682508912501632</v>
+        <v>-8.574238451570269</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3599768104210153</v>
+        <v>-0.3166686260484699</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.978194005568603</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.926466775552223</v>
+        <v>1.906258458258398</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.97917025431183</v>
+        <v>-8.870899793380467</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4748623712158864</v>
+        <v>-0.431554186843341</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.046937141302482</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.888999870041104</v>
+        <v>1.868791552747279</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.412519362422065</v>
+        <v>-9.304248901490702</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6522283189943838</v>
+        <v>-0.6089201346218385</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.046937141302482</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.884973565506701</v>
+        <v>1.864765248212876</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.795520751164696</v>
+        <v>-9.687250290233333</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8055309758130202</v>
+        <v>-0.7622227914404749</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.046937141302482</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.884871464185117</v>
+        <v>1.864663146891292</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.952919631377817</v>
+        <v>-9.844649170446454</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8659190119268385</v>
+        <v>-0.8226108275542932</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.204336021515603</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.793003652028674</v>
+        <v>1.772795334734849</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.31244995388182</v>
+        <v>-10.20417949295046</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.004380837630388</v>
+        <v>-0.9610726532578431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.204336021515603</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.798353955326724</v>
+        <v>1.778145638032899</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.63884998254683</v>
+        <v>-10.53057952161547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.127024829139217</v>
+        <v>-1.083716644766672</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.530736050180616</v>
+        <v>-2.564416579003658</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.610429958084894</v>
+        <v>1.590221640791069</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.85799895062103</v>
+        <v>-10.74972848968967</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.211642665747127</v>
+        <v>-1.168334481374581</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.749885018254814</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.481982327862145</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.85430802566462</v>
+        <v>-10.74603756473326</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.210166295764563</v>
+        <v>-1.166858111392017</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.749885018254814</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.481982327862145</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.05856620099448</v>
+        <v>-10.95029574006312</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.286356368777866</v>
+        <v>-1.24304818440532</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.877523962868803</v>
+        <v>-2.911204491691844</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.410912158212394</v>
+        <v>1.390703840918569</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.27660397262566</v>
+        <v>-11.1683335116943</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.3690889229459</v>
+        <v>-1.325780738573355</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.052294730964701</v>
+        <v>-3.085975259787743</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.31053225183929</v>
+        <v>1.290323934545465</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.20313414095821</v>
+        <v>-11.09486368002685</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.3243292887855</v>
+        <v>-1.281021104412955</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.978824899297253</v>
+        <v>-3.012505428120295</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.36998585233318</v>
+        <v>1.349777535039355</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.37825855834475</v>
+        <v>-11.26998809741339</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.3798238349926</v>
+        <v>-1.336515650620055</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.153949316683797</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.279466422648771</v>
+        <v>1.259258105354946</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.61271065235924</v>
+        <v>-11.50444019142788</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.480823837499992</v>
+        <v>-1.437515653127447</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.153949316683797</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.272247257747175</v>
+        <v>1.25203894045335</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.90051449689648</v>
+        <v>-11.79224403596512</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.602617566088864</v>
+        <v>-1.559309381716318</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.441753161221035</v>
+        <v>-3.475433690044077</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.092892760250856</v>
+        <v>1.072684442957031</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.13033894406031</v>
+        <v>-12.02206848312894</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.693431555115837</v>
+        <v>-1.650123370743292</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.604400698291196</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9964200278473161</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.36236786379657</v>
+        <v>-12.25409740286521</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.783549394381228</v>
+        <v>-1.740241210008682</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.666413395479619</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9619061381633767</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.31035234982776</v>
+        <v>-12.20208188889639</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.758752853107302</v>
+        <v>-1.715444668734756</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.666413395479619</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9658964738497775</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.45202419155188</v>
+        <v>-12.34375373062051</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.816896816695691</v>
+        <v>-1.773588632323146</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.666413395479619</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9644212469510358</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.55093093201115</v>
+        <v>-12.44266047107979</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.841406102714529</v>
+        <v>-1.798097918341984</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.765320135938894</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9201306128403428</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.35177882477405</v>
+        <v>-12.24350836384269</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.774796393466373</v>
+        <v>-1.731488209093828</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.599997609989081</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.006272994763548</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.12593367205464</v>
+        <v>-12.01766321112328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.6748792593424</v>
+        <v>-1.631571074969854</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.558070934401917</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.041008073152054</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.83965885973195</v>
+        <v>-11.73138839880058</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.559230189857263</v>
+        <v>-1.515922005484717</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.558070934401917</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.042147217708113</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.89255414777623</v>
+        <v>-11.78428368684487</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.57775453091287</v>
+        <v>-1.534446346540324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.553115588313471</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.047754199523289</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.60864541684749</v>
+        <v>-11.50037495591612</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.458457334302734</v>
+        <v>-1.415149149930188</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.553115588313471</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.053487903761925</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.49322449270939</v>
+        <v>-11.38495403177802</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.422026227041361</v>
+        <v>-1.378718042668814</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.437694664175376</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.113003195850918</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.22938762550532</v>
+        <v>-11.12111716457395</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.32637496147264</v>
+        <v>-1.283066777100094</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.437694664175376</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.10311971453801</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.96214582463692</v>
+        <v>-10.85387536370556</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.221312801624655</v>
+        <v>-1.178004617252109</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.437694664175376</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.101285154038636</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.8388398961587</v>
+        <v>-10.73056943522734</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.172290745206829</v>
+        <v>-1.128982560834282</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.348276993047813</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.154635441741713</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.81488635518274</v>
+        <v>-10.70661589425138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.162040822670952</v>
+        <v>-1.118732638298405</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.324323452071855</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.169676072472781</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.55082641685995</v>
+        <v>-10.44255595592858</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.069677163503584</v>
+        <v>-1.026368979131039</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.060263513749059</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.314851719304707</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.843746793355111</v>
+        <v>-9.735476332423746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7896323477619509</v>
+        <v>-0.7463241633894047</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.060263513749059</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.312064685644406</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.80356249498892</v>
+        <v>-9.695292034057555</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7732150045276334</v>
+        <v>-0.7299068201550871</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.020079215382868</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.336518888551962</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.723492699451116</v>
+        <v>-9.615222238519751</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7418202650917545</v>
+        <v>-0.6985120807192082</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.940009419845064</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.383927587095401</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.490011477221518</v>
+        <v>-9.381741016290153</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6405033473620629</v>
+        <v>-0.5971951629895171</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.706528197615465</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.531940749271013</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.310302947077645</v>
+        <v>-9.20203248614628</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.571512145617473</v>
+        <v>-0.5282039612449267</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.649356693452769</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.563351441455671</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.178027473446758</v>
+        <v>-9.069757012515392</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.523234469418091</v>
+        <v>-0.4799262850455448</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.517081219821883</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.63808421238123</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.987427798773604</v>
+        <v>-8.879157337842239</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4441795388611927</v>
+        <v>-0.4008713544886469</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.32648154514873</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.755259077872758</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.738428000090023</v>
+        <v>-8.630157539158658</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3316732781641014</v>
+        <v>-0.2883650937915556</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.32648154514873</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.768165419096417</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.844017989863127</v>
+        <v>-8.735747528931762</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5018852036725621</v>
+        <v>-0.4585770193000158</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.432071534921835</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.576835495633336</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.862752891981724</v>
+        <v>-8.754482431050359</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4608348226429144</v>
+        <v>-0.4175266382703686</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.432071534921835</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.625379837510422</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.714812850574125</v>
+        <v>-8.60654238964276</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5215377287680423</v>
+        <v>-0.4782295443954965</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.411750619013277</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.517693464367389</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.690584214185153</v>
+        <v>-8.582313753253787</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5205602604659316</v>
+        <v>-0.4772520760933854</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.387521982624305</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.523516659947294</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.647035807414461</v>
+        <v>-8.538765346483096</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5101015098527482</v>
+        <v>-0.4667933254802019</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.387521982624305</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.516556047852201</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.404887413960603</v>
+        <v>-8.429248565181787</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3987797980900618</v>
+        <v>-0.4085242585785354</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.387521982624305</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.531018402233344</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.341658042192256</v>
+        <v>-8.36601919341344</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3789559289235278</v>
+        <v>-0.3887003894120014</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.387521982624305</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.525550522692539</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.155170349815249</v>
+        <v>-8.179531501036433</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3068627579621483</v>
+        <v>-0.3166072184506219</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.201034290247299</v>
+        <v>-2.23471481907034</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.63494123212932</v>
+        <v>1.614732914835495</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.134021150911806</v>
+        <v>-8.158382302132988</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.290702100163446</v>
+        <v>-0.3004465606519187</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.179885091343855</v>
+        <v>-2.213565620166897</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.655331729708711</v>
+        <v>1.635123412414886</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.890255708928362</v>
+        <v>-7.914616860149544</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1974152150230175</v>
+        <v>-0.2071596755114906</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.179885091343855</v>
+        <v>-2.213565620166897</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.651112438055762</v>
+        <v>1.630904120761937</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.626227641735102</v>
+        <v>-7.650588792956285</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08967967422569778</v>
+        <v>-0.09942413471417044</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.978019692527902</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.77435599126535</v>
+        <v>1.754147673971525</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.376377247786028</v>
+        <v>-7.40073839900721</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.003002558337634298</v>
+        <v>-0.006741902150838808</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.978019692527902</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.767098066249052</v>
+        <v>1.746889748955227</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.072809758782049</v>
+        <v>-7.097170910003231</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1280286774598745</v>
+        <v>0.1182842169714018</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.978019692527902</v>
+        <v>-2.011700221350944</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.770697189769701</v>
+        <v>1.750488872475876</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.999329849930035</v>
+        <v>-7.023691001151217</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1707481470552339</v>
+        <v>0.1610036865667608</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.904539783675887</v>
+        <v>-1.938220312498929</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.828112641135463</v>
+        <v>1.807904323841638</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.774296850261212</v>
+        <v>-6.798658001482394</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.25978182453906</v>
+        <v>0.2500373640505869</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.679506784007065</v>
+        <v>-1.713187312830106</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.962152918553054</v>
+        <v>1.941944601259229</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.559662472624805</v>
+        <v>-6.584023623845987</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.35033037664794</v>
+        <v>0.3405859161594669</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.464872406370658</v>
+        <v>-1.498552935193699</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.095628346189215</v>
+        <v>2.07542002889539</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.293062115650454</v>
+        <v>-6.317423266871636</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4381647782214761</v>
+        <v>0.4284203177330035</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.464872406370658</v>
+        <v>-1.498552935193699</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.076822604973011</v>
+        <v>2.056614287679186</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.052631618845593</v>
+        <v>-6.076992770066775</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5360800535682979</v>
+        <v>0.5263355930798248</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.224441909565797</v>
+        <v>-1.258122438388839</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.222823979680804</v>
+        <v>2.202615662386979</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.809840811196148</v>
+        <v>-5.83420196241733</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6371256904628964</v>
+        <v>0.6273812299744232</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.224441909565797</v>
+        <v>-1.258122438388839</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.226753293515625</v>
+        <v>2.206544976221799</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.693900961570963</v>
+        <v>-5.718262112792145</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6841802142303104</v>
+        <v>0.6744357537418373</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.147620178549674</v>
+        <v>-1.181300707372715</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.273524916042639</v>
+        <v>2.253316598748814</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.451245373147799</v>
+        <v>-5.475606524368981</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7782405208195691</v>
+        <v>0.7684960603310964</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.147620178549674</v>
+        <v>-1.181300707372715</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.270522987262632</v>
+        <v>2.250314669968807</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.231224575110788</v>
+        <v>-5.255585726331971</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8678278770449874</v>
+        <v>0.8580834165565148</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.006400333481693</v>
+        <v>-1.040080862304735</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.356833931314035</v>
+        <v>2.33662561402021</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.031975945205979</v>
+        <v>-5.056337096427161</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9634215118087344</v>
+        <v>0.9536770513202617</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.006400333481693</v>
+        <v>-1.040080862304735</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.372728114115858</v>
+        <v>2.352519796822033</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.87246084168661</v>
+        <v>-4.896821992907792</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.028373397656784</v>
+        <v>1.018628937168311</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8468852299623234</v>
+        <v>-0.8805657587853651</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.469583020667782</v>
+        <v>2.449374703373957</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.727788696586872</v>
+        <v>-4.752149847808054</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.096330358258119</v>
+        <v>1.086585897769646</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.702213084862586</v>
+        <v>-0.7358936136856278</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.566474410289064</v>
+        <v>2.546266092995239</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.710019237655916</v>
+        <v>-4.734380388877098</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.018777833917223</v>
+        <v>1.00903337342875</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6844436259316304</v>
+        <v>-0.7181241547546722</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.492475777734359</v>
+        <v>2.472267460440534</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.623219739876907</v>
+        <v>-4.647580891098089</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.075898126351393</v>
+        <v>1.06615366586292</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6844436259316304</v>
+        <v>-0.7181241547546722</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.514876271056925</v>
+        <v>2.4946679537631</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.523527125147895</v>
+        <v>-4.547888276369077</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.11584757361641</v>
+        <v>1.106103113127937</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5847510112026186</v>
+        <v>-0.6184315400256604</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.574764241267744</v>
+        <v>2.554555923973919</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.591897311471905</v>
+        <v>-4.616258462693088</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.099506421561508</v>
+        <v>1.089761961073035</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5754753121664037</v>
+        <v>-0.6091558409894454</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.591336583164175</v>
+        <v>2.57112826587035</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.470480881845429</v>
+        <v>-4.494842033066611</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.13850970204399</v>
+        <v>1.128765241555517</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5754753121664037</v>
+        <v>-0.6091558409894454</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.581773291796067</v>
+        <v>2.561564974502241</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.501474041174134</v>
+        <v>-4.525835192395316</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9508220033528942</v>
+        <v>0.9410775428644214</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5754753121664037</v>
+        <v>-0.6091558409894454</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.406482856836453</v>
+        <v>2.386274539542628</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.325999781381665</v>
+        <v>-4.350360932602847</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.02557893926167</v>
+        <v>1.015834478773197</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5754753121664037</v>
+        <v>-0.6091558409894454</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.411050088828241</v>
+        <v>2.390841771534416</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.436936034022914</v>
+        <v>-4.461297185244096</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9812159120919679</v>
+        <v>0.971471451603495</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5754753121664037</v>
+        <v>-0.6091558409894454</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.411061562715039</v>
+        <v>2.390853245421213</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.639962611566147</v>
+        <v>-4.664323762787329</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9031366662945801</v>
+        <v>0.8933922058061072</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7785018897096371</v>
+        <v>-0.8121824185326788</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.292377001409004</v>
+        <v>2.272168684115179</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.482037012630854</v>
+        <v>-4.506398163852036</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9764792923008296</v>
+        <v>0.966734831812357</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7785018897096371</v>
+        <v>-0.8121824185326788</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.302549387841136</v>
+        <v>2.282341070547312</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.630358266441982</v>
+        <v>-4.654719417663165</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9120970613502386</v>
+        <v>0.9023526008617657</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7785018897096371</v>
+        <v>-0.8121824185326788</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.297495658414997</v>
+        <v>2.277287341121172</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.631541351093043</v>
+        <v>-4.655902502314225</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9033996029343399</v>
+        <v>0.893655142445867</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7841449381761486</v>
+        <v>-0.8178254669991903</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.285885604779616</v>
+        <v>2.26567728748579</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.50841364409896</v>
+        <v>-4.532774795320142</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9532025587650748</v>
+        <v>0.9434580982766019</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7841449381761486</v>
+        <v>-0.8178254669991903</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.286437477812717</v>
+        <v>2.266229160518892</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.565276278750032</v>
+        <v>3.435893733366089</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.70556945131942</v>
+        <v>2.75412790330595</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.50841364409896</v>
+        <v>-4.402466032782573</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9532025587650748</v>
+        <v>0.9927850658791741</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7841449381761486</v>
+        <v>-0.6875167044616211</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.698633248305788</v>
+        <v>2.341617880628978</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240426.xlsx
+++ b/tame_output/ON/bt/strategyON_20240426.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.3%</t>
+          <t>-695.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>410.0%</t>
+          <t>399.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.8%</t>
+          <t>-615.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-278.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.9%</t>
+          <t>-282.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-167.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-292.7%</t>
+          <t>-308.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-211.9%</t>
+          <t>-221.2%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2655523161318096</v>
+        <v>0.3109731026351032</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.224354691630253</v>
+        <v>3.24252300623157</v>
       </c>
       <c r="F1837" t="n">
         <v>1.653857716665527</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.217330049284726</v>
+        <v>0.2627508357880197</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.209145767513086</v>
+        <v>3.227314082114403</v>
       </c>
       <c r="F1838" t="n">
         <v>1.605635449818444</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.01980144256506905</v>
+        <v>0.02561934393822457</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.149234255270709</v>
+        <v>3.167402569872027</v>
       </c>
       <c r="F1839" t="n">
         <v>1.605635449818444</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.01476385183748252</v>
+        <v>0.0306569346658111</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.149826731747082</v>
+        <v>3.1679950463484</v>
       </c>
       <c r="F1840" t="n">
         <v>1.661279906084761</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1773899318021211</v>
+        <v>-0.1319691452988275</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.063522681384964</v>
+        <v>3.081690995986281</v>
       </c>
       <c r="F1841" t="n">
         <v>1.498653826120122</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2431573218515332</v>
+        <v>-0.1977365353482395</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.038233334495669</v>
+        <v>3.056401649096987</v>
       </c>
       <c r="F1842" t="n">
         <v>1.498653826120122</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.2566928056282428</v>
+        <v>-0.2112720191249491</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.023447172972741</v>
+        <v>3.041615487574058</v>
       </c>
       <c r="F1843" t="n">
         <v>1.498653826120122</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3384647060559944</v>
+        <v>-0.2930439195527008</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.980821138756879</v>
+        <v>2.998989453358196</v>
       </c>
       <c r="F1844" t="n">
         <v>1.525689399526259</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4056738139278721</v>
+        <v>-0.3602530274245785</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.95870281244183</v>
+        <v>2.976871127043147</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.613239598319484</v>
+        <v>-0.5678188118161904</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.873501294804425</v>
+        <v>2.891669609405743</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.030993621866321</v>
+        <v>-0.9855728353630274</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.704326576890754</v>
+        <v>2.722494891492071</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.252615555424438</v>
+        <v>-1.207194768921145</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.615544020066428</v>
+        <v>2.633712334667746</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.460619613777516</v>
+        <v>-1.415198827274222</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.537234541279123</v>
+        <v>2.55540285588044</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.672032034665491</v>
+        <v>-1.626611248162197</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.447751029261921</v>
+        <v>2.465919343863238</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.011190412254013</v>
+        <v>-1.965769625750719</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.305171977532961</v>
+        <v>2.323340292134279</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.339207633981492</v>
+        <v>-2.293786847478199</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.194303378580738</v>
+        <v>2.212471693182055</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.83253250551667</v>
+        <v>-2.787111719013377</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005072180375235</v>
+        <v>2.023240494976553</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324917533540767</v>
+        <v>-3.279496747037474</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809224561209329</v>
+        <v>1.827392875810646</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.71009792447084</v>
+        <v>-3.664677137967546</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.653694943650163</v>
+        <v>1.67186325825148</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053780697697502</v>
+        <v>-4.008359911194209</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.517990957814114</v>
+        <v>1.536159272415431</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.41143104793585</v>
+        <v>-4.366010261432557</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.371036876375032</v>
+        <v>1.38920519097635</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.720665150931901</v>
+        <v>-4.675244364428607</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.249116161876872</v>
+        <v>1.267284476478189</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.152470944081688</v>
+        <v>-5.107050157578395</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.062726732084361</v>
+        <v>1.080895046685679</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.387164938214241</v>
+        <v>-5.341744151710947</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.957133909433431</v>
+        <v>0.9753022240347482</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.722827585444693</v>
+        <v>-5.6774067989414</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8214494421972152</v>
+        <v>0.8396177567985323</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.086453830345007</v>
+        <v>-6.041033043841713</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6824865044713313</v>
+        <v>0.7006548190726485</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.451581212983753</v>
+        <v>-6.40616042648046</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5356900664216639</v>
+        <v>0.5538583810229816</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.860169990164431</v>
+        <v>-6.814749203661139</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3710160995641516</v>
+        <v>0.3891844141654688</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.273152474305525</v>
+        <v>-7.227731687802232</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2010085383791749</v>
+        <v>0.2191768529804921</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.689544348592523</v>
+        <v>-7.64412356208923</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.03244583927325317</v>
+        <v>0.05061415387457036</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.066221359122366</v>
+        <v>-8.020800572619073</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1079662742700052</v>
+        <v>-0.08979795966868798</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.412096181107175</v>
+        <v>-8.366675394603883</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2502166379182338</v>
+        <v>-0.2320483233169166</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.574238451570269</v>
+        <v>-8.528817665066976</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3166686260484699</v>
+        <v>-0.2985003114471527</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.870899793380467</v>
+        <v>-8.825479006877174</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.431554186843341</v>
+        <v>-0.4133858722420238</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.304248901490702</v>
+        <v>-9.258828114987409</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6089201346218385</v>
+        <v>-0.5907518200205213</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.687250290233333</v>
+        <v>-9.64182950373004</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7622227914404749</v>
+        <v>-0.7440544768391577</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.844649170446454</v>
+        <v>-9.799228383943161</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8226108275542932</v>
+        <v>-0.804442512952976</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20417949295046</v>
+        <v>-10.15875870644716</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9610726532578431</v>
+        <v>-0.9429043386565263</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53057952161547</v>
+        <v>-10.48515873511218</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.083716644766672</v>
+        <v>-1.065548330165354</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.74972848968967</v>
+        <v>-10.70430770318637</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.168334481374581</v>
+        <v>-1.150166166773265</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74603756473326</v>
+        <v>-10.70061677822996</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.166858111392017</v>
+        <v>-1.1486897967907</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95029574006312</v>
+        <v>-10.90487495355983</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24304818440532</v>
+        <v>-1.224879869804003</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1683335116943</v>
+        <v>-11.122912725191</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.325780738573355</v>
+        <v>-1.307612423972038</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09486368002685</v>
+        <v>-11.04944289352355</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.281021104412955</v>
+        <v>-1.262852789811637</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.26998809741339</v>
+        <v>-11.2245673109101</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.336515650620055</v>
+        <v>-1.318347336018737</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50444019142788</v>
+        <v>-11.45901940492459</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.437515653127447</v>
+        <v>-1.419347338526129</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79224403596512</v>
+        <v>-11.74682324946183</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.559309381716318</v>
+        <v>-1.541141067115002</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02206848312894</v>
+        <v>-11.97664769662565</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.650123370743292</v>
+        <v>-1.631955056141975</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25409740286521</v>
+        <v>-12.20867661636191</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.740241210008682</v>
+        <v>-1.722072895407365</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.70009392430266</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20208188889639</v>
+        <v>-12.1566611023931</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.715444668734756</v>
+        <v>-1.697276354133439</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.70009392430266</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34375373062051</v>
+        <v>-12.29833294411722</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.773588632323146</v>
+        <v>-1.755420317721829</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.70009392430266</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44266047107979</v>
+        <v>-12.3972396845765</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.798097918341984</v>
+        <v>-1.779929603740667</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.799000664761936</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24350836384269</v>
+        <v>-12.1980875773394</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.731488209093828</v>
+        <v>-1.71331989449251</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.633678138812123</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.01766321112328</v>
+        <v>-11.97224242461999</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.631571074969854</v>
+        <v>-1.613402760368536</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.591751463224959</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73138839880058</v>
+        <v>-11.68596761229729</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.515922005484717</v>
+        <v>-1.4977536908834</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.591751463224959</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78428368684487</v>
+        <v>-11.73886290034158</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.534446346540324</v>
+        <v>-1.516278031939007</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.586796117136513</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50037495591612</v>
+        <v>-11.45495416941283</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.415149149930188</v>
+        <v>-1.396980835328871</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.586796117136513</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.38495403177802</v>
+        <v>-11.33953324527473</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.378718042668814</v>
+        <v>-1.360549728067498</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.471375192998417</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.12111716457395</v>
+        <v>-11.07569637807066</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.283066777100094</v>
+        <v>-1.264898462498777</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.471375192998417</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.85387536370556</v>
+        <v>-10.80845457720226</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.178004617252109</v>
+        <v>-1.159836302650791</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.471375192998417</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.73056943522734</v>
+        <v>-10.68514864872405</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.128982560834282</v>
+        <v>-1.110814246232965</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.381957521870854</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.70661589425138</v>
+        <v>-10.66119510774809</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.118732638298405</v>
+        <v>-1.100564323697089</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.358003980894897</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.44255595592858</v>
+        <v>-10.39713516942529</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.026368979131039</v>
+        <v>-1.008200664529721</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.093944042572101</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.735476332423746</v>
+        <v>-9.690055545920453</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7463241633894047</v>
+        <v>-0.7281558487880875</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.093944042572101</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.695292034057555</v>
+        <v>-9.649871247554263</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7299068201550871</v>
+        <v>-0.7117385055537699</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.05375974420591</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.615222238519751</v>
+        <v>-9.569801452016458</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6985120807192082</v>
+        <v>-0.6803437661178915</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.973689948668106</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.381741016290153</v>
+        <v>-9.33632022978686</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5971951629895171</v>
+        <v>-0.5790268483882</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.740208726438507</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.20203248614628</v>
+        <v>-9.156611699642987</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5282039612449267</v>
+        <v>-0.5100356466436096</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.683037222275811</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.069757012515392</v>
+        <v>-9.0243362260121</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4799262850455448</v>
+        <v>-0.4617579704442276</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.550761748644925</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.879157337842239</v>
+        <v>-8.833736551338946</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4008713544886469</v>
+        <v>-0.3827030398873297</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.360162073971772</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.630157539158658</v>
+        <v>-8.584736752655365</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2883650937915556</v>
+        <v>-0.2701967791902384</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.360162073971772</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.735747528931762</v>
+        <v>-8.69032674242847</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4585770193000158</v>
+        <v>-0.4404087046986991</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.465752063744877</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.754482431050359</v>
+        <v>-8.709061644547067</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4175266382703686</v>
+        <v>-0.3993583236690514</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.465752063744877</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.60654238964276</v>
+        <v>-8.561121603139467</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4782295443954965</v>
+        <v>-0.4600612297941793</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.445431147836319</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.582313753253787</v>
+        <v>-8.536892966750495</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4772520760933854</v>
+        <v>-0.4590837614920682</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.421202511447347</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.538765346483096</v>
+        <v>-8.493344559979803</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4667933254802019</v>
+        <v>-0.4486250108788852</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.421202511447347</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.429248565181787</v>
+        <v>-8.383827778678494</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4085242585785354</v>
+        <v>-0.3903559439772182</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.421202511447347</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.36601919341344</v>
+        <v>-8.320598406910147</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3887003894120014</v>
+        <v>-0.3705320748106842</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.421202511447347</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.179531501036433</v>
+        <v>-8.13411071453314</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3166072184506219</v>
+        <v>-0.2984389038493047</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.23471481907034</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.158382302132988</v>
+        <v>-8.112961515629696</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3004465606519187</v>
+        <v>-0.2822782460506019</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.213565620166897</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.914616860149544</v>
+        <v>-7.869196073646251</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2071596755114906</v>
+        <v>-0.1889913609101734</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.213565620166897</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.650588792956285</v>
+        <v>-7.605168006452992</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.09942413471417044</v>
+        <v>-0.0812558201128537</v>
       </c>
       <c r="F1918" t="n">
         <v>-2.011700221350944</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.40073839900721</v>
+        <v>-7.355317612503917</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.006741902150838808</v>
+        <v>0.01142641245047837</v>
       </c>
       <c r="F1919" t="n">
         <v>-2.011700221350944</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.097170910003231</v>
+        <v>-7.051750123499938</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1182842169714018</v>
+        <v>0.1364525315727185</v>
       </c>
       <c r="F1920" t="n">
         <v>-2.011700221350944</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.023691001151217</v>
+        <v>-6.978270214647925</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1610036865667608</v>
+        <v>0.179172001168078</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.938220312498929</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.798658001482394</v>
+        <v>-6.753237214979102</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2500373640505869</v>
+        <v>0.268205678651904</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.713187312830106</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.584023623845987</v>
+        <v>-6.538602837342695</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3405859161594669</v>
+        <v>0.3587542307607841</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.498552935193699</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.317423266871636</v>
+        <v>-6.272002480368343</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4284203177330035</v>
+        <v>0.4465886323343207</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.498552935193699</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.076992770066775</v>
+        <v>-6.031571983563483</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5263355930798248</v>
+        <v>0.544503907681142</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.258122438388839</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.83420196241733</v>
+        <v>-5.788781175914037</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6273812299744232</v>
+        <v>0.6455495445757404</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.258122438388839</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.718262112792145</v>
+        <v>-5.672841326288852</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6744357537418373</v>
+        <v>0.6926040683431545</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.181300707372715</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.475606524368981</v>
+        <v>-5.430185737865688</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7684960603310964</v>
+        <v>0.7866643749324136</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.181300707372715</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.255585726331971</v>
+        <v>-5.210164939828678</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8580834165565148</v>
+        <v>0.8762517311578319</v>
       </c>
       <c r="F1929" t="n">
         <v>-1.040080862304735</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.056337096427161</v>
+        <v>-5.010916309923869</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9536770513202617</v>
+        <v>0.9718453659215789</v>
       </c>
       <c r="F1930" t="n">
         <v>-1.040080862304735</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.896821992907792</v>
+        <v>-4.851401206404499</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.018628937168311</v>
+        <v>1.036797251769629</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.8805657587853651</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.752149847808054</v>
+        <v>-4.706729061304761</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.086585897769646</v>
+        <v>1.104754212370963</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.7358936136856278</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.734380388877098</v>
+        <v>-4.688959602373806</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.00903337342875</v>
+        <v>1.027201688030067</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.7181241547546722</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144511</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.647580891098089</v>
+        <v>-4.602160104594796</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.06615366586292</v>
+        <v>1.084321980464237</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.7181241547546722</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.547888276369077</v>
+        <v>-4.502467489865785</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.106103113127937</v>
+        <v>1.124271427729254</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.6184315400256604</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.616258462693088</v>
+        <v>-4.570837676189795</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.089761961073035</v>
+        <v>1.107930275674352</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.6091558409894454</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.494842033066611</v>
+        <v>-4.449421246563318</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.128765241555517</v>
+        <v>1.146933556156834</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.6091558409894454</v>
@@ -46125,10 +46125,10 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.525835192395316</v>
+        <v>-4.480414405892024</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9410775428644214</v>
+        <v>0.9592458574657385</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.6091558409894454</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.350360932602847</v>
+        <v>-4.304940146099554</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.015834478773197</v>
+        <v>1.034002793374514</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.6091558409894454</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.461297185244096</v>
+        <v>-4.415876398740803</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.971471451603495</v>
+        <v>0.9896397662048122</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.6091558409894454</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.664323762787329</v>
+        <v>-4.618902976284036</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8933922058061072</v>
+        <v>0.9115605204074244</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.8121824185326788</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734154</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.506398163852036</v>
+        <v>-4.460977377348743</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.966734831812357</v>
+        <v>0.9849031464136739</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.8121824185326788</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212291</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.654719417663165</v>
+        <v>-4.609298631159872</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9023526008617657</v>
+        <v>0.9205209154630829</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.8121824185326788</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786038</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.655902502314225</v>
+        <v>-4.610481715810932</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.893655142445867</v>
+        <v>0.9118234570471841</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.8178254669991903</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273184</v>
       </c>
       <c r="C1945" t="n">
         <v>2.756924440718406</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.532774795320142</v>
+        <v>-4.487354008816849</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9434580982766019</v>
+        <v>0.9616264128779188</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.8178254669991903</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.435893733366089</v>
+        <v>3.796053096534711</v>
       </c>
       <c r="C1946" t="n">
         <v>2.75412790330595</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.402466032782573</v>
+        <v>-4.534139709278987</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9927850658791741</v>
+        <v>0.9401155952806084</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6875167044616211</v>
+        <v>-0.8436167900593603</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.341617880628978</v>
+        <v>2.247957829270335</v>
       </c>
     </row>
   </sheetData>
